--- a/output/pdf_financials_xlsx/VHI.xlsx
+++ b/output/pdf_financials_xlsx/VHI.xlsx
@@ -4275,34 +4275,34 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.09293</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.142733</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.413539</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.664818</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.851368</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.221221</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.300142</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.895066</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.017775</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.124799</v>
       </c>
     </row>
     <row r="93">
@@ -7953,7 +7953,11 @@
           <t>Share-based payment reserve (Note 13 (c))</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8700,7 +8704,11 @@
           <t>Share-based payment reserve (Note 14 (c))</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -8834,7 +8842,11 @@
           <t>Warrant reserve (Note 14 (e))</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -11142,7 +11154,11 @@
           <t>Share-based payment reserve (Note 15(c))</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -11211,7 +11227,11 @@
           <t>Warrant reserve (Note 15 (d))</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -12639,7 +12659,11 @@
           <t>Share‐based payment reserve 15(c)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -13773,7 +13797,11 @@
           <t>Share‐based payment reserve 17(c)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -14765,7 +14793,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -14836,7 +14868,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -15499,7 +15535,11 @@
           <t>Reserves (notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -47016,7 +47056,7 @@
         </is>
       </c>
       <c r="F582" s="5" t="n">
-        <v>0.151969</v>
+        <v>-0.151969</v>
       </c>
       <c r="G582" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VHI.xlsx
+++ b/output/pdf_financials_xlsx/VHI.xlsx
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.029548</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.040914</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.489566</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1563,13 +1563,13 @@
         <v>-1.58443</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.531133</v>
+        <v>-1.501585</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.336148</v>
+        <v>1.295234</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.399714</v>
+        <v>5.88928</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.938763</v>
@@ -1647,13 +1647,13 @@
         <v>-0.067229</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.710118</v>
+        <v>0.739666</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.615951</v>
+        <v>4.575037</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.658827</v>
+        <v>10.148393</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>11.087781</v>
@@ -1689,13 +1689,13 @@
         <v>-0.6573083648255501</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.879098795589289</v>
+        <v>2.998898056010898</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>11.54830371980916</v>
+        <v>11.44594403306372</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>18.39485827554342</v>
+        <v>19.32721757616292</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>16.16428680454691</v>
@@ -1807,22 +1807,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.052937</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.14337</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.543281</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.805993</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.995691</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>16.389982</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>17.45221</v>
@@ -1891,22 +1891,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.052937</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.14337</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.543281</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.805993</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.995691</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>16.389982</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>17.45221</v>
@@ -2395,22 +2395,22 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.05855</v>
+        <v>0.005613</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.163134</v>
+        <v>0.019764</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.631568</v>
+        <v>0.088287</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.709603</v>
+        <v>1.90361</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.2753</v>
+        <v>0.279609</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>22.423973</v>
+        <v>6.033991</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>12.409955</v>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -35749,7 +35749,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -44915,7 +44915,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -45698,7 +45698,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">

--- a/output/pdf_financials_xlsx/VHI.xlsx
+++ b/output/pdf_financials_xlsx/VHI.xlsx
@@ -1599,25 +1599,25 @@
         <v>0.04845</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.357928</v>
+        <v>1.179728</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.517201</v>
+        <v>1.695466</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.241251</v>
+        <v>2.676157</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.279803</v>
+        <v>3.872953</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>4.259113</v>
+        <v>4.977694</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.149018</v>
+        <v>5.962924</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>9.809967</v>
+        <v>11.081525</v>
       </c>
     </row>
     <row r="29">
@@ -1641,25 +1641,25 @@
         <v>-2.35262</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.411614</v>
+        <v>0.233414</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.067229</v>
+        <v>0.111036</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.739666</v>
+        <v>1.174572</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.575037</v>
+        <v>5.168187</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>10.148393</v>
+        <v>10.866974</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>11.087781</v>
+        <v>11.901687</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>15.781714</v>
+        <v>17.053272</v>
       </c>
     </row>
     <row r="30">
@@ -1683,25 +1683,25 @@
         <v>-205.2196850812681</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.51636192867112</v>
+        <v>2.561093896754826</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.6573083648255501</v>
+        <v>1.085616201293635</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.998898056010898</v>
+        <v>4.762178723159956</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>11.44594403306372</v>
+        <v>12.92990180285045</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.32721757616292</v>
+        <v>20.69572698776106</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>16.16428680454691</v>
+        <v>17.35083711753934</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>14.48303236400611</v>
+        <v>15.64995350240153</v>
       </c>
     </row>
     <row r="31">
@@ -4582,28 +4582,28 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.04409</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.357928</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.77275</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.676157</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>3.872953</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>4.977694</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>5.962924</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>11.081525</v>
       </c>
     </row>
     <row r="101">
@@ -5092,22 +5092,22 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.00174</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.001593</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.001057</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>-0.000141</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.00588</v>
       </c>
     </row>
     <row r="113">
@@ -15825,7 +15825,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -15888,7 +15892,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -15957,7 +15965,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -16091,7 +16099,11 @@
           <t>Loss on disposal of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -20034,7 +20046,11 @@
           <t>Depreciation of right-of-use assets (Note 13)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -23134,7 +23150,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -23205,7 +23225,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -23276,7 +23296,11 @@
           <t>Depreciation on right-of-use assets (Note 17)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -23418,7 +23442,11 @@
           <t>Loss on disposal of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -25696,7 +25724,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -30103,7 +30131,11 @@
           <t>Depreciation of property and equipment (Note 6) 165,796 123,147</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -30172,7 +30204,11 @@
           <t>Depreciation of right-of-use assets 156,655 111,156</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -30584,7 +30620,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -32555,7 +32591,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -32620,7 +32660,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -32969,7 +33013,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -35195,7 +35239,11 @@
           <t>Depreciation of right-of-use assets (Note 13)</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -35546,7 +35594,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -39551,7 +39599,11 @@
           <t>Depreciation of right-of-use assets (Note 17)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -39831,7 +39883,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
